--- a/youtube-automation/data/vehicles_tracker.xlsx
+++ b/youtube-automation/data/vehicles_tracker.xlsx
@@ -4171,19 +4171,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17 12:30:31</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_91_Skoda_Slavia\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4211,19 +4211,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17 12:38:12</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_92_Skoda_Kushaq\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4251,19 +4251,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19 03:42:58</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_93_Skoda_Kodiaq\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4291,19 +4291,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19 03:46:34</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_94_Skoda_Superb\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4331,19 +4331,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19 03:51:07</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_95_MG_Hector\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7757,6 +7757,181 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Skoda Slavia</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Crystal Blue with Crystalline Split Tail Lamps and Hexagonal Grille</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:30:31</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_91_Skoda_Slavia\video.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Skoda Kushaq</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Tornado Red with Signature Butterfly Grille and Two-Tone Machine Alloys</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:38:12</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_92_Skoda_Kushaq\video.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Skoda Kodiaq</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Lava Blue Metallic with Panoramic Sunroof and Illuminated Grille Ribs</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:42:58</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_93_Skoda_Kodiaq\video.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Skoda Superb</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Rosso Brunello Wine Metallic with Executive Matrix LED Lights</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:34</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_94_Skoda_Superb\video.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>MG Hector</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Candy White with Argyle Inspired Diamond Mesh Grille and Connected LEDs</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:07</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_95_MG_Hector\video.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/youtube-automation/data/vehicles_tracker.xlsx
+++ b/youtube-automation/data/vehicles_tracker.xlsx
@@ -4371,19 +4371,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20 00:51:08</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_96_MG_Astor\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4411,19 +4411,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20 00:56:39</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_97_Mahindra_Scorpio_Classic\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4451,19 +4451,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20 01:00:16</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_98_Hyundai_Grand_i10_Nios\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7932,6 +7932,111 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>MG Astor</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Spiced Orange with Celestial Diamond Grille and Full LED Hawkeye Lamps</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:51:08</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_96_MG_Astor\video.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Mahindra Scorpio Classic</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Galaxy Grey with Vertical Chrome Slats and Classic Spoiler</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:56:39</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_97_Mahindra_Scorpio_Classic\video.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Hyundai Grand i10 Nios</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Spark Green with Black Roof and Boomerang DRLs</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 01:00:16</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_98_Hyundai_Grand_i10_Nios\video.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/youtube-automation/data/vehicles_tracker.xlsx
+++ b/youtube-automation/data/vehicles_tracker.xlsx
@@ -45,7 +45,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="007F6000"/>
+      <color rgb="00783F04"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -70,8 +70,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">

--- a/youtube-automation/data/vehicles_tracker.xlsx
+++ b/youtube-automation/data/vehicles_tracker.xlsx
@@ -4491,19 +4491,19 @@
           <t>1:18</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21 00:12:11</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_99_MG_ZS_EV\video.mp4</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8037,6 +8037,41 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>MG ZS EV</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Ferrite White with Integrated Aero Wheel Covers and Grille-Less Front</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:12:11</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>D:\Temp\yt automation\youtube-automation\output\100_popular_cars_in_India_99_MG_ZS_EV\video.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
